--- a/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.005639999999999999</v>
+        <v>-0.0272</v>
       </c>
       <c r="E2">
-        <v>-0.0009700000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="F2">
-        <v>0.0531</v>
+        <v>0.195</v>
       </c>
       <c r="G2">
-        <v>0.0324290845196059</v>
+        <v>0.09094814835683396</v>
       </c>
       <c r="H2">
-        <v>0.0324290845196059</v>
+        <v>0.09094814835683396</v>
       </c>
       <c r="I2">
-        <v>0.0655414889642149</v>
+        <v>0.07169570790663606</v>
       </c>
       <c r="J2">
-        <v>0.05886800520190488</v>
+        <v>0.05750156262451894</v>
       </c>
       <c r="K2">
-        <v>90.39999999999998</v>
+        <v>1168.3</v>
       </c>
       <c r="L2">
-        <v>0.003042961636467067</v>
+        <v>0.04114253919510923</v>
       </c>
       <c r="M2">
-        <v>508.6</v>
+        <v>1393.9</v>
       </c>
       <c r="N2">
-        <v>0.01698588962177507</v>
+        <v>0.04391923825848043</v>
       </c>
       <c r="O2">
-        <v>5.626106194690267</v>
+        <v>1.193101087049559</v>
       </c>
       <c r="P2">
-        <v>508.6</v>
+        <v>1220.7</v>
       </c>
       <c r="Q2">
-        <v>0.01698588962177507</v>
+        <v>0.03846202320261644</v>
       </c>
       <c r="R2">
-        <v>5.626106194690267</v>
+        <v>1.044851493623213</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>173.2</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1242556854867638</v>
       </c>
       <c r="U2">
-        <v>4227.1</v>
+        <v>4057.2</v>
       </c>
       <c r="V2">
-        <v>0.1411739166736245</v>
+        <v>0.1278349476019132</v>
       </c>
       <c r="W2">
-        <v>-0.04313818440388718</v>
+        <v>0.05105810502039335</v>
       </c>
       <c r="X2">
-        <v>0.05374147118888602</v>
+        <v>0.0862799710695408</v>
       </c>
       <c r="Y2">
-        <v>-0.0968796555927732</v>
+        <v>-0.03522186604914745</v>
       </c>
       <c r="Z2">
-        <v>0.884569117988602</v>
+        <v>0.8136107983278751</v>
       </c>
       <c r="AA2">
-        <v>0.05171806490945069</v>
+        <v>0.05503403915676792</v>
       </c>
       <c r="AB2">
-        <v>0.04654646771814377</v>
+        <v>0.07718789528406386</v>
       </c>
       <c r="AC2">
-        <v>0.008257423362738867</v>
+        <v>-0.0224080049025076</v>
       </c>
       <c r="AD2">
-        <v>21205.2</v>
+        <v>21696</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21205.2</v>
+        <v>21696</v>
       </c>
       <c r="AG2">
-        <v>16978.1</v>
+        <v>17638.8</v>
       </c>
       <c r="AH2">
-        <v>0.4145875572117613</v>
+        <v>0.4060351313213734</v>
       </c>
       <c r="AI2">
-        <v>0.4707768132673223</v>
+        <v>0.4988182495378757</v>
       </c>
       <c r="AJ2">
-        <v>0.3618474614561621</v>
+        <v>0.3572299429284317</v>
       </c>
       <c r="AK2">
-        <v>0.4159677968634772</v>
+        <v>0.4472584538612897</v>
       </c>
       <c r="AL2">
-        <v>653.1</v>
+        <v>515.4</v>
       </c>
       <c r="AM2">
-        <v>653.1</v>
+        <v>515.4</v>
       </c>
       <c r="AN2">
-        <v>9.258295494236814</v>
+        <v>9.713467048710601</v>
       </c>
       <c r="AO2">
-        <v>2.981319859133364</v>
+        <v>3.950135816841289</v>
       </c>
       <c r="AP2">
-        <v>7.412722668529514</v>
+        <v>7.897027220630372</v>
       </c>
       <c r="AQ2">
-        <v>2.981319859133364</v>
+        <v>3.950135816841289</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QBE Insurance Group Limited (ASX:QBE)</t>
+          <t>Insurance Australia Group Limited (ASX:IAG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,43 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.012</v>
+        <v>-0.0272</v>
+      </c>
+      <c r="E3">
+        <v>-0.179</v>
+      </c>
+      <c r="F3">
+        <v>0.195</v>
       </c>
       <c r="G3">
-        <v>-0.04390429168249146</v>
+        <v>0.08977847616127549</v>
       </c>
       <c r="H3">
-        <v>-0.04390429168249146</v>
+        <v>0.08977847616127549</v>
       </c>
       <c r="I3">
-        <v>0.05028484618306114</v>
+        <v>0.08450866165874599</v>
       </c>
       <c r="J3">
-        <v>0.05028484618306114</v>
+        <v>0.06352285144240788</v>
       </c>
       <c r="K3">
-        <v>-364</v>
+        <v>239.1</v>
       </c>
       <c r="L3">
-        <v>-0.02764906950246867</v>
+        <v>0.04581864172926568</v>
       </c>
       <c r="M3">
-        <v>58</v>
+        <v>322.4</v>
       </c>
       <c r="N3">
-        <v>0.004759794508181923</v>
+        <v>0.04100320496515236</v>
       </c>
       <c r="O3">
-        <v>-0.1593406593406593</v>
+        <v>1.348389795064826</v>
       </c>
       <c r="P3">
-        <v>58</v>
+        <v>322.4</v>
       </c>
       <c r="Q3">
-        <v>0.004759794508181923</v>
+        <v>0.04100320496515236</v>
       </c>
       <c r="R3">
-        <v>-0.1593406593406593</v>
+        <v>1.348389795064826</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>767</v>
+        <v>646.3</v>
       </c>
       <c r="V3">
-        <v>0.06294417909957818</v>
+        <v>0.08219718166556442</v>
       </c>
       <c r="W3">
-        <v>-0.04313818440388718</v>
+        <v>0.05105810502039335</v>
       </c>
       <c r="X3">
-        <v>0.05374147118888602</v>
+        <v>0.08626513097157305</v>
       </c>
       <c r="Y3">
-        <v>-0.0968796555927732</v>
+        <v>-0.03520702595117971</v>
       </c>
       <c r="Z3">
-        <v>1.216166281755196</v>
+        <v>1.744001069447229</v>
       </c>
       <c r="AA3">
-        <v>0.06115473441108545</v>
+        <v>0.1107839208498968</v>
       </c>
       <c r="AB3">
-        <v>0.04674464573238378</v>
+        <v>0.07718789528406386</v>
       </c>
       <c r="AC3">
-        <v>0.01441008867870167</v>
+        <v>0.03359602556583297</v>
       </c>
       <c r="AD3">
-        <v>3138</v>
+        <v>1780.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3138</v>
+        <v>1780.4</v>
       </c>
       <c r="AG3">
-        <v>2371</v>
+        <v>1134.1</v>
       </c>
       <c r="AH3">
-        <v>0.2047848388738792</v>
+        <v>0.1846275095404015</v>
       </c>
       <c r="AI3">
-        <v>0.2619802972115545</v>
+        <v>0.2844634754265994</v>
       </c>
       <c r="AJ3">
-        <v>0.1628836800307769</v>
+        <v>0.1260545298936301</v>
       </c>
       <c r="AK3">
-        <v>0.2114887164392115</v>
+        <v>0.2020668151447662</v>
       </c>
       <c r="AL3">
-        <v>189</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AM3">
-        <v>189</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AN3">
-        <v>4.189586114819759</v>
+        <v>3.800213447171825</v>
       </c>
       <c r="AO3">
-        <v>3.502645502645503</v>
+        <v>6.879875195007801</v>
       </c>
       <c r="AP3">
-        <v>3.165554072096128</v>
+        <v>2.420704375667023</v>
       </c>
       <c r="AQ3">
-        <v>3.502645502645503</v>
+        <v>6.879875195007801</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Suncorp Group Limited (ASX:SUN)</t>
+          <t>QBE Insurance Group Limited (ASX:QBE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,124 +862,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0153</v>
+        <v>0.017</v>
       </c>
       <c r="E4">
-        <v>-0.0009700000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="F4">
-        <v>0.0437</v>
+        <v>0.199</v>
       </c>
       <c r="G4">
-        <v>0.1578902834579044</v>
+        <v>0.08972762645914396</v>
       </c>
       <c r="H4">
-        <v>0.1578902834579044</v>
+        <v>0.08972762645914396</v>
       </c>
       <c r="I4">
-        <v>0.1443613970761059</v>
+        <v>0.05859922178988327</v>
       </c>
       <c r="J4">
-        <v>0.1002644385914831</v>
+        <v>0.0480102396067991</v>
       </c>
       <c r="K4">
-        <v>774.5</v>
+        <v>460</v>
       </c>
       <c r="L4">
-        <v>0.07281530578667794</v>
+        <v>0.0357976653696498</v>
       </c>
       <c r="M4">
-        <v>320.9</v>
+        <v>346</v>
       </c>
       <c r="N4">
-        <v>0.0315756329394169</v>
+        <v>0.02552827293117696</v>
       </c>
       <c r="O4">
-        <v>0.4143318269851517</v>
+        <v>0.7521739130434782</v>
       </c>
       <c r="P4">
-        <v>320.9</v>
+        <v>345</v>
       </c>
       <c r="Q4">
-        <v>0.0315756329394169</v>
+        <v>0.02545449179553771</v>
       </c>
       <c r="R4">
-        <v>0.4143318269851517</v>
+        <v>0.75</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.002890173410404624</v>
       </c>
       <c r="U4">
-        <v>1962.1</v>
+        <v>801</v>
       </c>
       <c r="V4">
-        <v>0.1930649716124335</v>
+        <v>0.05909868964703104</v>
       </c>
       <c r="W4">
-        <v>0.08789350643455367</v>
+        <v>0.05204208620884716</v>
       </c>
       <c r="X4">
-        <v>0.08423354939722508</v>
+        <v>0.0862799710695408</v>
       </c>
       <c r="Y4">
-        <v>0.00365995703732859</v>
+        <v>-0.03423788486069364</v>
       </c>
       <c r="Z4">
-        <v>0.515816630861222</v>
+        <v>1.146297948260482</v>
       </c>
       <c r="AA4">
-        <v>0.05171806490945069</v>
+        <v>0.05503403915676792</v>
       </c>
       <c r="AB4">
-        <v>0.04346064154671182</v>
+        <v>0.07744204405927552</v>
       </c>
       <c r="AC4">
-        <v>0.008257423362738867</v>
+        <v>-0.0224080049025076</v>
       </c>
       <c r="AD4">
-        <v>16138.9</v>
+        <v>3076</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>16138.9</v>
+        <v>3076</v>
       </c>
       <c r="AG4">
-        <v>14176.8</v>
+        <v>2275</v>
       </c>
       <c r="AH4">
-        <v>0.6136043920948376</v>
+        <v>0.1849713763409824</v>
       </c>
       <c r="AI4">
-        <v>0.6154858245555157</v>
+        <v>0.2654241090689447</v>
       </c>
       <c r="AJ4">
-        <v>0.5824558232024224</v>
+        <v>0.1437271773877664</v>
       </c>
       <c r="AK4">
-        <v>0.5843861941605899</v>
+        <v>0.210882461994809</v>
       </c>
       <c r="AL4">
-        <v>397.4</v>
+        <v>186</v>
       </c>
       <c r="AM4">
-        <v>397.4</v>
+        <v>186</v>
       </c>
       <c r="AN4">
-        <v>9.609920209598666</v>
+        <v>3.825870646766169</v>
       </c>
       <c r="AO4">
-        <v>3.86386512330146</v>
+        <v>4.048387096774194</v>
       </c>
       <c r="AP4">
-        <v>8.441586280814576</v>
+        <v>2.829601990049751</v>
       </c>
       <c r="AQ4">
-        <v>3.86386512330146</v>
+        <v>4.048387096774194</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +990,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Insurance Australia Group Limited (ASX:IAG)</t>
+          <t>Suncorp Group Limited (ASX:SUN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,121 +999,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.005639999999999999</v>
+        <v>-0.0293</v>
+      </c>
+      <c r="E5">
+        <v>-0.0873</v>
       </c>
       <c r="F5">
-        <v>0.0625</v>
+        <v>0.0291</v>
       </c>
       <c r="G5">
-        <v>-0.02336448598130841</v>
+        <v>0.09305770720371805</v>
       </c>
       <c r="H5">
-        <v>-0.02336448598130841</v>
+        <v>0.09305770720371805</v>
       </c>
       <c r="I5">
-        <v>-0.04239469050521469</v>
+        <v>0.08151626646010844</v>
       </c>
       <c r="J5">
-        <v>-0.04239469050521469</v>
+        <v>0.06807392739238464</v>
       </c>
       <c r="K5">
-        <v>-320.1</v>
+        <v>469.2</v>
       </c>
       <c r="L5">
-        <v>-0.05419544900446974</v>
+        <v>0.04542989930286599</v>
       </c>
       <c r="M5">
-        <v>129.7</v>
+        <v>725.5</v>
       </c>
       <c r="N5">
-        <v>0.01707882331252798</v>
+        <v>0.07029085201619936</v>
       </c>
       <c r="O5">
-        <v>-0.4051858794126835</v>
+        <v>1.546248934356351</v>
       </c>
       <c r="P5">
-        <v>129.7</v>
+        <v>553.3</v>
       </c>
       <c r="Q5">
-        <v>0.01707882331252798</v>
+        <v>0.05360706880849497</v>
       </c>
       <c r="R5">
-        <v>-0.4051858794126835</v>
+        <v>1.17924126172208</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>172.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.2373535492763612</v>
       </c>
       <c r="U5">
-        <v>1498</v>
+        <v>2609.9</v>
       </c>
       <c r="V5">
-        <v>0.1972558004793132</v>
+        <v>0.2528629837037611</v>
       </c>
       <c r="W5">
-        <v>-0.07629239459446577</v>
+        <v>0.04661930547965622</v>
       </c>
       <c r="X5">
-        <v>0.05365887941117281</v>
+        <v>0.126562754203187</v>
       </c>
       <c r="Y5">
-        <v>-0.1299512740056386</v>
+        <v>-0.07994344872353075</v>
       </c>
       <c r="Z5">
-        <v>2.761419421197812</v>
+        <v>0.4989492499818836</v>
       </c>
       <c r="AA5">
-        <v>-0.1170695217167703</v>
+        <v>0.03396543501575151</v>
       </c>
       <c r="AB5">
-        <v>0.04654646771814377</v>
+        <v>0.07027198200481477</v>
       </c>
       <c r="AC5">
-        <v>-0.1636159894349141</v>
+        <v>-0.03630654698906326</v>
       </c>
       <c r="AD5">
-        <v>1928.3</v>
+        <v>16839.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1928.3</v>
+        <v>16839.6</v>
       </c>
       <c r="AG5">
-        <v>430.3</v>
+        <v>14229.7</v>
       </c>
       <c r="AH5">
-        <v>0.2024993436597532</v>
+        <v>0.6199919001509516</v>
       </c>
       <c r="AI5">
-        <v>0.2817669063066222</v>
+        <v>0.6565914142004913</v>
       </c>
       <c r="AJ5">
-        <v>0.05362327870895382</v>
+        <v>0.579595211619846</v>
       </c>
       <c r="AK5">
-        <v>0.08049610894941633</v>
+        <v>0.6176862539121678</v>
       </c>
       <c r="AL5">
-        <v>66.7</v>
+        <v>265.3</v>
       </c>
       <c r="AM5">
-        <v>66.7</v>
+        <v>265.3</v>
       </c>
       <c r="AN5">
-        <v>-13.9731884057971</v>
+        <v>17.52117365518676</v>
       </c>
       <c r="AO5">
-        <v>-3.754122938530735</v>
+        <v>3.173388616660384</v>
       </c>
       <c r="AP5">
-        <v>-3.118115942028985</v>
+        <v>14.80563937155343</v>
       </c>
       <c r="AQ5">
-        <v>-3.754122938530735</v>
+        <v>3.173388616660384</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0272</v>
+        <v>0.0528</v>
       </c>
       <c r="E2">
-        <v>-0.13</v>
+        <v>-0.002150000000000001</v>
       </c>
       <c r="F2">
-        <v>0.195</v>
+        <v>0.083</v>
       </c>
       <c r="G2">
-        <v>0.09094814835683396</v>
+        <v>0.1402153446467728</v>
       </c>
       <c r="H2">
-        <v>0.09094814835683396</v>
+        <v>0.1402153446467728</v>
       </c>
       <c r="I2">
-        <v>0.07169570790663606</v>
+        <v>0.1743642148917914</v>
       </c>
       <c r="J2">
-        <v>0.05750156262451894</v>
+        <v>0.1263169413945731</v>
       </c>
       <c r="K2">
-        <v>1168.3</v>
+        <v>2439.8</v>
       </c>
       <c r="L2">
-        <v>0.04114253919510923</v>
+        <v>0.07268924587663267</v>
       </c>
       <c r="M2">
-        <v>1393.9</v>
+        <v>1083.6</v>
       </c>
       <c r="N2">
-        <v>0.04391923825848043</v>
+        <v>0.0298630038830724</v>
       </c>
       <c r="O2">
-        <v>1.193101087049559</v>
+        <v>0.4441347651446839</v>
       </c>
       <c r="P2">
-        <v>1220.7</v>
+        <v>1001.4</v>
       </c>
       <c r="Q2">
-        <v>0.03846202320261644</v>
+        <v>0.0275976486604916</v>
       </c>
       <c r="R2">
-        <v>1.044851493623213</v>
+        <v>0.4104434789736863</v>
       </c>
       <c r="S2">
-        <v>173.2</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1242556854867638</v>
+        <v>0.07585825027685493</v>
       </c>
       <c r="U2">
-        <v>4057.2</v>
+        <v>5370.7</v>
       </c>
       <c r="V2">
-        <v>0.1278349476019132</v>
+        <v>0.1480114755950691</v>
       </c>
       <c r="W2">
-        <v>0.05105810502039335</v>
+        <v>0.1303989449390043</v>
       </c>
       <c r="X2">
-        <v>0.0862799710695408</v>
+        <v>0.07377555862976722</v>
       </c>
       <c r="Y2">
-        <v>-0.03522186604914745</v>
+        <v>0.05662338630923709</v>
       </c>
       <c r="Z2">
-        <v>0.8136107983278751</v>
+        <v>0.9876270034397224</v>
       </c>
       <c r="AA2">
-        <v>0.05503403915676792</v>
+        <v>0.1873020473223342</v>
       </c>
       <c r="AB2">
-        <v>0.07718789528406386</v>
+        <v>0.06688856090879018</v>
       </c>
       <c r="AC2">
-        <v>-0.0224080049025076</v>
+        <v>0.1203171008208073</v>
       </c>
       <c r="AD2">
-        <v>21696</v>
+        <v>23200.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21696</v>
+        <v>23200.4</v>
       </c>
       <c r="AG2">
-        <v>17638.8</v>
+        <v>17829.7</v>
       </c>
       <c r="AH2">
-        <v>0.4060351313213734</v>
+        <v>0.3900138015435539</v>
       </c>
       <c r="AI2">
-        <v>0.4988182495378757</v>
+        <v>0.5067459390036935</v>
       </c>
       <c r="AJ2">
-        <v>0.3572299429284317</v>
+        <v>0.3294755282230197</v>
       </c>
       <c r="AK2">
-        <v>0.4472584538612897</v>
+        <v>0.4411937920044343</v>
       </c>
       <c r="AL2">
-        <v>515.4</v>
+        <v>1273.9</v>
       </c>
       <c r="AM2">
-        <v>515.4</v>
+        <v>1126.9</v>
       </c>
       <c r="AN2">
-        <v>9.713467048710601</v>
+        <v>3.846028877874111</v>
       </c>
       <c r="AO2">
-        <v>3.950135816841289</v>
+        <v>4.594159667163828</v>
       </c>
       <c r="AP2">
-        <v>7.897027220630372</v>
+        <v>2.95570512076654</v>
       </c>
       <c r="AQ2">
-        <v>3.950135816841289</v>
+        <v>5.193451060431271</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0272</v>
+        <v>0.0177</v>
       </c>
       <c r="E3">
-        <v>-0.179</v>
+        <v>-0.0206</v>
       </c>
       <c r="F3">
-        <v>0.195</v>
+        <v>0.083</v>
       </c>
       <c r="G3">
-        <v>0.08977847616127549</v>
+        <v>0.1759142496847415</v>
       </c>
       <c r="H3">
-        <v>0.08977847616127549</v>
+        <v>0.1759142496847415</v>
       </c>
       <c r="I3">
-        <v>0.08450866165874599</v>
+        <v>0.1714835895163764</v>
       </c>
       <c r="J3">
-        <v>0.06352285144240788</v>
+        <v>0.117157618802966</v>
       </c>
       <c r="K3">
-        <v>239.1</v>
+        <v>553.7</v>
       </c>
       <c r="L3">
-        <v>0.04581864172926568</v>
+        <v>0.09435602058552879</v>
       </c>
       <c r="M3">
-        <v>322.4</v>
+        <v>260.9</v>
       </c>
       <c r="N3">
-        <v>0.04100320496515236</v>
+        <v>0.02832359901860738</v>
       </c>
       <c r="O3">
-        <v>1.348389795064826</v>
+        <v>0.471193787249413</v>
       </c>
       <c r="P3">
-        <v>322.4</v>
+        <v>179.7</v>
       </c>
       <c r="Q3">
-        <v>0.04100320496515236</v>
+        <v>0.01950843519986104</v>
       </c>
       <c r="R3">
-        <v>1.348389795064826</v>
+        <v>0.3245439768827885</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>81.19999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.3112303564584132</v>
       </c>
       <c r="U3">
-        <v>646.3</v>
+        <v>900.5</v>
       </c>
       <c r="V3">
-        <v>0.08219718166556442</v>
+        <v>0.09775929826085068</v>
       </c>
       <c r="W3">
-        <v>0.05105810502039335</v>
+        <v>0.1303989449390043</v>
       </c>
       <c r="X3">
-        <v>0.08626513097157305</v>
+        <v>0.07322495548707161</v>
       </c>
       <c r="Y3">
-        <v>-0.03520702595117971</v>
+        <v>0.05717398945193269</v>
       </c>
       <c r="Z3">
-        <v>1.744001069447229</v>
+        <v>1.708205979099351</v>
       </c>
       <c r="AA3">
-        <v>0.1107839208498968</v>
+        <v>0.200129344936269</v>
       </c>
       <c r="AB3">
-        <v>0.07718789528406386</v>
+        <v>0.06688856090879018</v>
       </c>
       <c r="AC3">
-        <v>0.03359602556583297</v>
+        <v>0.1332407840274788</v>
       </c>
       <c r="AD3">
-        <v>1780.4</v>
+        <v>1754.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1780.4</v>
+        <v>1754.4</v>
       </c>
       <c r="AG3">
-        <v>1134.1</v>
+        <v>853.9000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1846275095404015</v>
+        <v>0.1599883273450182</v>
       </c>
       <c r="AI3">
-        <v>0.2844634754265994</v>
+        <v>0.2721730091996463</v>
       </c>
       <c r="AJ3">
-        <v>0.1260545298936301</v>
+        <v>0.08483602078427868</v>
       </c>
       <c r="AK3">
-        <v>0.2020668151447662</v>
+        <v>0.1539834818047391</v>
       </c>
       <c r="AL3">
-        <v>64.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AM3">
-        <v>64.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AN3">
-        <v>3.800213447171825</v>
+        <v>1.699505957570474</v>
       </c>
       <c r="AO3">
-        <v>6.879875195007801</v>
+        <v>10.4279792746114</v>
       </c>
       <c r="AP3">
-        <v>2.420704375667023</v>
+        <v>0.8271820207304079</v>
       </c>
       <c r="AQ3">
-        <v>6.879875195007801</v>
+        <v>10.4279792746114</v>
       </c>
     </row>
     <row r="4">
@@ -862,124 +862,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.017</v>
-      </c>
-      <c r="E4">
-        <v>-0.13</v>
+        <v>0.0538</v>
       </c>
       <c r="F4">
-        <v>0.199</v>
+        <v>0.214</v>
       </c>
       <c r="G4">
-        <v>0.08972762645914396</v>
+        <v>0.08371552225308443</v>
       </c>
       <c r="H4">
-        <v>0.08972762645914396</v>
+        <v>0.08371552225308443</v>
       </c>
       <c r="I4">
-        <v>0.05859922178988327</v>
+        <v>0.1663975195400814</v>
       </c>
       <c r="J4">
-        <v>0.0480102396067991</v>
+        <v>0.1305101210817143</v>
       </c>
       <c r="K4">
-        <v>460</v>
+        <v>1122</v>
       </c>
       <c r="L4">
-        <v>0.0357976653696498</v>
+        <v>0.07247593824688328</v>
       </c>
       <c r="M4">
-        <v>346</v>
+        <v>434</v>
       </c>
       <c r="N4">
-        <v>0.02552827293117696</v>
+        <v>0.0287765968027477</v>
       </c>
       <c r="O4">
-        <v>0.7521739130434782</v>
+        <v>0.3868092691622103</v>
       </c>
       <c r="P4">
-        <v>345</v>
+        <v>433</v>
       </c>
       <c r="Q4">
-        <v>0.02545449179553771</v>
+        <v>0.02871029128016072</v>
       </c>
       <c r="R4">
-        <v>0.75</v>
+        <v>0.3859180035650624</v>
       </c>
       <c r="S4">
         <v>1</v>
       </c>
       <c r="T4">
-        <v>0.002890173410404624</v>
+        <v>0.002304147465437788</v>
       </c>
       <c r="U4">
-        <v>801</v>
+        <v>767</v>
       </c>
       <c r="V4">
-        <v>0.05909868964703104</v>
+        <v>0.0508563358242108</v>
       </c>
       <c r="W4">
-        <v>0.05204208620884716</v>
+        <v>0.1318139097744361</v>
       </c>
       <c r="X4">
-        <v>0.0862799710695408</v>
+        <v>0.07377555862976722</v>
       </c>
       <c r="Y4">
-        <v>-0.03423788486069364</v>
+        <v>0.05803835114466886</v>
       </c>
       <c r="Z4">
-        <v>1.146297948260482</v>
+        <v>1.435153425419486</v>
       </c>
       <c r="AA4">
-        <v>0.05503403915676792</v>
+        <v>0.1873020473223342</v>
       </c>
       <c r="AB4">
-        <v>0.07744204405927552</v>
+        <v>0.06698494650152688</v>
       </c>
       <c r="AC4">
-        <v>-0.0224080049025076</v>
+        <v>0.1203171008208073</v>
       </c>
       <c r="AD4">
-        <v>3076</v>
+        <v>3263</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3076</v>
+        <v>3263</v>
       </c>
       <c r="AG4">
-        <v>2275</v>
+        <v>2496</v>
       </c>
       <c r="AH4">
-        <v>0.1849713763409824</v>
+        <v>0.1778715378283646</v>
       </c>
       <c r="AI4">
-        <v>0.2654241090689447</v>
+        <v>0.2659114986553663</v>
       </c>
       <c r="AJ4">
-        <v>0.1437271773877664</v>
+        <v>0.1419980998651701</v>
       </c>
       <c r="AK4">
-        <v>0.210882461994809</v>
+        <v>0.2169680111265647</v>
       </c>
       <c r="AL4">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>186</v>
+        <v>-147</v>
       </c>
       <c r="AN4">
-        <v>3.825870646766169</v>
-      </c>
-      <c r="AO4">
-        <v>4.048387096774194</v>
+        <v>1.244469870327994</v>
       </c>
       <c r="AP4">
-        <v>2.829601990049751</v>
+        <v>0.9519450800915332</v>
       </c>
       <c r="AQ4">
-        <v>4.048387096774194</v>
+        <v>-17.52380952380953</v>
       </c>
     </row>
     <row r="5">
@@ -999,124 +993,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0293</v>
+        <v>0.0528</v>
       </c>
       <c r="E5">
-        <v>-0.0873</v>
+        <v>0.0163</v>
       </c>
       <c r="F5">
-        <v>0.0291</v>
+        <v>0.0495</v>
       </c>
       <c r="G5">
-        <v>0.09305770720371805</v>
+        <v>0.1946691116277547</v>
       </c>
       <c r="H5">
-        <v>0.09305770720371805</v>
+        <v>0.1946691116277547</v>
       </c>
       <c r="I5">
-        <v>0.08151626646010844</v>
+        <v>0.1858443302007269</v>
       </c>
       <c r="J5">
-        <v>0.06807392739238464</v>
+        <v>0.1311692275657217</v>
       </c>
       <c r="K5">
-        <v>469.2</v>
+        <v>764.1</v>
       </c>
       <c r="L5">
-        <v>0.04542989930286599</v>
+        <v>0.06255116408526802</v>
       </c>
       <c r="M5">
-        <v>725.5</v>
+        <v>388.7</v>
       </c>
       <c r="N5">
-        <v>0.07029085201619936</v>
+        <v>0.03241165385320947</v>
       </c>
       <c r="O5">
-        <v>1.546248934356351</v>
+        <v>0.5087030493390917</v>
       </c>
       <c r="P5">
-        <v>553.3</v>
+        <v>388.7</v>
       </c>
       <c r="Q5">
-        <v>0.05360706880849497</v>
+        <v>0.03241165385320947</v>
       </c>
       <c r="R5">
-        <v>1.17924126172208</v>
+        <v>0.5087030493390917</v>
       </c>
       <c r="S5">
-        <v>172.2</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.2373535492763612</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>2609.9</v>
+        <v>3703.2</v>
       </c>
       <c r="V5">
-        <v>0.2528629837037611</v>
+        <v>0.3087904207594683</v>
       </c>
       <c r="W5">
-        <v>0.04661930547965622</v>
+        <v>0.0869609751101096</v>
       </c>
       <c r="X5">
-        <v>0.126562754203187</v>
+        <v>0.1014134419459159</v>
       </c>
       <c r="Y5">
-        <v>-0.07994344872353075</v>
+        <v>-0.01445246683580635</v>
       </c>
       <c r="Z5">
-        <v>0.4989492499818836</v>
+        <v>0.6181045387845975</v>
       </c>
       <c r="AA5">
-        <v>0.03396543501575151</v>
+        <v>0.08107629490724233</v>
       </c>
       <c r="AB5">
-        <v>0.07027198200481477</v>
+        <v>0.06056270730923632</v>
       </c>
       <c r="AC5">
-        <v>-0.03630654698906326</v>
+        <v>0.02051358759800601</v>
       </c>
       <c r="AD5">
-        <v>16839.6</v>
+        <v>18183</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>16839.6</v>
+        <v>18183</v>
       </c>
       <c r="AG5">
-        <v>14229.7</v>
+        <v>14479.8</v>
       </c>
       <c r="AH5">
-        <v>0.6199919001509516</v>
+        <v>0.6025729397261363</v>
       </c>
       <c r="AI5">
-        <v>0.6565914142004913</v>
+        <v>0.6717972969977315</v>
       </c>
       <c r="AJ5">
-        <v>0.579595211619846</v>
+        <v>0.5469772291140962</v>
       </c>
       <c r="AK5">
-        <v>0.6176862539121678</v>
+        <v>0.6197748576809485</v>
       </c>
       <c r="AL5">
-        <v>265.3</v>
+        <v>1177.4</v>
       </c>
       <c r="AM5">
-        <v>265.3</v>
+        <v>1177.4</v>
       </c>
       <c r="AN5">
-        <v>17.52117365518676</v>
+        <v>7.646341463414634</v>
       </c>
       <c r="AO5">
-        <v>3.173388616660384</v>
+        <v>1.928146764056395</v>
       </c>
       <c r="AP5">
-        <v>14.80563937155343</v>
+        <v>6.089066442388561</v>
       </c>
       <c r="AQ5">
-        <v>3.173388616660384</v>
+        <v>1.928146764056395</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0528</v>
+        <v>0.119</v>
       </c>
       <c r="E2">
-        <v>-0.002150000000000001</v>
+        <v>0.288</v>
       </c>
       <c r="F2">
-        <v>0.083</v>
+        <v>0.0818</v>
       </c>
       <c r="G2">
-        <v>0.1402153446467728</v>
+        <v>0.1039710135897761</v>
       </c>
       <c r="H2">
-        <v>0.1402153446467728</v>
+        <v>0.1039710135897761</v>
       </c>
       <c r="I2">
-        <v>0.1743642148917914</v>
+        <v>0.1125643723085845</v>
       </c>
       <c r="J2">
-        <v>0.1263169413945731</v>
+        <v>0.08078011269471805</v>
       </c>
       <c r="K2">
-        <v>2439.8</v>
+        <v>3154.7</v>
       </c>
       <c r="L2">
-        <v>0.07268924587663267</v>
+        <v>0.0755980723653783</v>
       </c>
       <c r="M2">
-        <v>1083.6</v>
+        <v>1690.2</v>
       </c>
       <c r="N2">
-        <v>0.0298630038830724</v>
+        <v>0.03737065534624569</v>
       </c>
       <c r="O2">
-        <v>0.4441347651446839</v>
+        <v>0.5357720226962944</v>
       </c>
       <c r="P2">
-        <v>1001.4</v>
+        <v>1392.6</v>
       </c>
       <c r="Q2">
-        <v>0.0275976486604916</v>
+        <v>0.03079066065269302</v>
       </c>
       <c r="R2">
-        <v>0.4104434789736863</v>
+        <v>0.4414365866801915</v>
       </c>
       <c r="S2">
-        <v>82.19999999999999</v>
+        <v>297.6</v>
       </c>
       <c r="T2">
-        <v>0.07585825027685493</v>
+        <v>0.1760738374156905</v>
       </c>
       <c r="U2">
-        <v>5370.7</v>
+        <v>3163</v>
       </c>
       <c r="V2">
-        <v>0.1480114755950691</v>
+        <v>0.06993455381622005</v>
       </c>
       <c r="W2">
-        <v>0.1303989449390043</v>
+        <v>0.1352981029810298</v>
       </c>
       <c r="X2">
-        <v>0.07377555862976722</v>
+        <v>0.07758269821044392</v>
       </c>
       <c r="Y2">
-        <v>0.05662338630923709</v>
+        <v>0.0577154047705859</v>
       </c>
       <c r="Z2">
-        <v>0.9876270034397224</v>
+        <v>1.188117656102748</v>
       </c>
       <c r="AA2">
-        <v>0.1873020473223342</v>
+        <v>0.176262748386754</v>
       </c>
       <c r="AB2">
-        <v>0.06688856090879018</v>
+        <v>0.07212885924977307</v>
       </c>
       <c r="AC2">
-        <v>0.1203171008208073</v>
+        <v>0.1041338891369809</v>
       </c>
       <c r="AD2">
-        <v>23200.4</v>
+        <v>6892.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23200.4</v>
+        <v>6892.4</v>
       </c>
       <c r="AG2">
-        <v>17829.7</v>
+        <v>3729.4</v>
       </c>
       <c r="AH2">
-        <v>0.3900138015435539</v>
+        <v>0.1322399674599581</v>
       </c>
       <c r="AI2">
-        <v>0.5067459390036935</v>
+        <v>0.2217325144848042</v>
       </c>
       <c r="AJ2">
-        <v>0.3294755282230197</v>
+        <v>0.07617643093791744</v>
       </c>
       <c r="AK2">
-        <v>0.4411937920044343</v>
+        <v>0.1335682794139241</v>
       </c>
       <c r="AL2">
-        <v>1273.9</v>
+        <v>289.4</v>
       </c>
       <c r="AM2">
-        <v>1126.9</v>
+        <v>289.4</v>
       </c>
       <c r="AN2">
-        <v>3.846028877874111</v>
+        <v>1.40727280151908</v>
       </c>
       <c r="AO2">
-        <v>4.594159667163828</v>
+        <v>16.23116793365584</v>
       </c>
       <c r="AP2">
-        <v>2.95570512076654</v>
+        <v>0.7614594605631214</v>
       </c>
       <c r="AQ2">
-        <v>5.193451060431271</v>
+        <v>16.23116793365584</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0177</v>
+        <v>0.154</v>
       </c>
       <c r="E3">
-        <v>-0.0206</v>
+        <v>-0.0355</v>
       </c>
       <c r="F3">
-        <v>0.083</v>
+        <v>0.0818</v>
       </c>
       <c r="G3">
-        <v>0.1759142496847415</v>
+        <v>0.1084132993477772</v>
       </c>
       <c r="H3">
-        <v>0.1759142496847415</v>
+        <v>0.1084132993477772</v>
       </c>
       <c r="I3">
-        <v>0.1714835895163764</v>
+        <v>0.1047867156458505</v>
       </c>
       <c r="J3">
-        <v>0.117157618802966</v>
+        <v>0.07259650625564953</v>
       </c>
       <c r="K3">
-        <v>553.7</v>
+        <v>599.1</v>
       </c>
       <c r="L3">
-        <v>0.09435602058552879</v>
+        <v>0.05614176474998125</v>
       </c>
       <c r="M3">
-        <v>260.9</v>
+        <v>602.5</v>
       </c>
       <c r="N3">
-        <v>0.02832359901860738</v>
+        <v>0.0486951321032256</v>
       </c>
       <c r="O3">
-        <v>0.471193787249413</v>
+        <v>1.00567517943582</v>
       </c>
       <c r="P3">
-        <v>179.7</v>
+        <v>306.9</v>
       </c>
       <c r="Q3">
-        <v>0.01950843519986104</v>
+        <v>0.02480420919913682</v>
       </c>
       <c r="R3">
-        <v>0.3245439768827885</v>
+        <v>0.5122684026039058</v>
       </c>
       <c r="S3">
-        <v>81.19999999999999</v>
+        <v>295.6</v>
       </c>
       <c r="T3">
-        <v>0.3112303564584132</v>
+        <v>0.4906224066390042</v>
       </c>
       <c r="U3">
-        <v>900.5</v>
+        <v>1228.3</v>
       </c>
       <c r="V3">
-        <v>0.09775929826085068</v>
+        <v>0.09927341205376265</v>
       </c>
       <c r="W3">
-        <v>0.1303989449390043</v>
+        <v>0.1352981029810298</v>
       </c>
       <c r="X3">
-        <v>0.07322495548707161</v>
+        <v>0.07758269821044392</v>
       </c>
       <c r="Y3">
-        <v>0.05717398945193269</v>
+        <v>0.0577154047705859</v>
       </c>
       <c r="Z3">
-        <v>1.708205979099351</v>
+        <v>3.140065913370999</v>
       </c>
       <c r="AA3">
-        <v>0.200129344936269</v>
+        <v>0.2279578147231896</v>
       </c>
       <c r="AB3">
-        <v>0.06688856090879018</v>
+        <v>0.07209558602393173</v>
       </c>
       <c r="AC3">
-        <v>0.1332407840274788</v>
+        <v>0.1558622286992578</v>
       </c>
       <c r="AD3">
-        <v>1754.4</v>
+        <v>1959.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1754.4</v>
+        <v>1959.6</v>
       </c>
       <c r="AG3">
-        <v>853.9000000000001</v>
+        <v>731.3</v>
       </c>
       <c r="AH3">
-        <v>0.1599883273450182</v>
+        <v>0.1367242281527996</v>
       </c>
       <c r="AI3">
-        <v>0.2721730091996463</v>
+        <v>0.292124446564601</v>
       </c>
       <c r="AJ3">
-        <v>0.08483602078427868</v>
+        <v>0.05580653530929015</v>
       </c>
       <c r="AK3">
-        <v>0.1539834818047391</v>
+        <v>0.133453775685244</v>
       </c>
       <c r="AL3">
-        <v>96.5</v>
+        <v>123.4</v>
       </c>
       <c r="AM3">
-        <v>96.5</v>
+        <v>123.4</v>
       </c>
       <c r="AN3">
-        <v>1.699505957570474</v>
+        <v>1.693836978131213</v>
       </c>
       <c r="AO3">
-        <v>10.4279792746114</v>
+        <v>9.061588330632091</v>
       </c>
       <c r="AP3">
-        <v>0.8271820207304079</v>
+        <v>0.632120321548967</v>
       </c>
       <c r="AQ3">
-        <v>10.4279792746114</v>
+        <v>9.061588330632091</v>
       </c>
     </row>
     <row r="4">
@@ -862,118 +862,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0538</v>
+        <v>0.119</v>
+      </c>
+      <c r="E4">
+        <v>0.288</v>
       </c>
       <c r="F4">
-        <v>0.214</v>
+        <v>0.106</v>
       </c>
       <c r="G4">
-        <v>0.08371552225308443</v>
+        <v>0.09597523219814241</v>
       </c>
       <c r="H4">
-        <v>0.08371552225308443</v>
+        <v>0.09597523219814241</v>
       </c>
       <c r="I4">
-        <v>0.1663975195400814</v>
+        <v>0.1186790505675955</v>
       </c>
       <c r="J4">
-        <v>0.1305101210817143</v>
+        <v>0.09096666809998855</v>
       </c>
       <c r="K4">
-        <v>1122</v>
+        <v>1757</v>
       </c>
       <c r="L4">
-        <v>0.07247593824688328</v>
+        <v>0.07883519540539329</v>
       </c>
       <c r="M4">
-        <v>434</v>
+        <v>626</v>
       </c>
       <c r="N4">
-        <v>0.0287765968027477</v>
+        <v>0.03499728854873065</v>
       </c>
       <c r="O4">
-        <v>0.3868092691622103</v>
+        <v>0.3562891291974957</v>
       </c>
       <c r="P4">
-        <v>433</v>
+        <v>624</v>
       </c>
       <c r="Q4">
-        <v>0.02871029128016072</v>
+        <v>0.03488547612525228</v>
       </c>
       <c r="R4">
-        <v>0.3859180035650624</v>
+        <v>0.3551508252703472</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>0.002304147465437788</v>
+        <v>0.003194888178913738</v>
       </c>
       <c r="U4">
-        <v>767</v>
+        <v>1445</v>
       </c>
       <c r="V4">
-        <v>0.0508563358242108</v>
+        <v>0.08078447596312427</v>
       </c>
       <c r="W4">
-        <v>0.1318139097744361</v>
+        <v>0.1950921607817011</v>
       </c>
       <c r="X4">
-        <v>0.07377555862976722</v>
+        <v>0.0778235041610951</v>
       </c>
       <c r="Y4">
-        <v>0.05803835114466886</v>
+        <v>0.117268656620606</v>
       </c>
       <c r="Z4">
-        <v>1.435153425419486</v>
+        <v>1.937663015127804</v>
       </c>
       <c r="AA4">
-        <v>0.1873020473223342</v>
+        <v>0.176262748386754</v>
       </c>
       <c r="AB4">
-        <v>0.06698494650152688</v>
+        <v>0.07212885924977307</v>
       </c>
       <c r="AC4">
-        <v>0.1203171008208073</v>
+        <v>0.1041338891369809</v>
       </c>
       <c r="AD4">
-        <v>3263</v>
+        <v>3048</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3263</v>
+        <v>3048</v>
       </c>
       <c r="AG4">
-        <v>2496</v>
+        <v>1603</v>
       </c>
       <c r="AH4">
-        <v>0.1778715378283646</v>
+        <v>0.1455928082502591</v>
       </c>
       <c r="AI4">
-        <v>0.2659114986553663</v>
+        <v>0.2304203205322044</v>
       </c>
       <c r="AJ4">
-        <v>0.1419980998651701</v>
+        <v>0.08224688431562692</v>
       </c>
       <c r="AK4">
-        <v>0.2169680111265647</v>
+        <v>0.1360434524314691</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="AM4">
-        <v>-147</v>
+        <v>166</v>
       </c>
       <c r="AN4">
-        <v>1.244469870327994</v>
+        <v>1.129725722757598</v>
+      </c>
+      <c r="AO4">
+        <v>15.93373493975904</v>
       </c>
       <c r="AP4">
-        <v>0.9519450800915332</v>
+        <v>0.5941438102297999</v>
       </c>
       <c r="AQ4">
-        <v>-17.52380952380953</v>
+        <v>15.93373493975904</v>
       </c>
     </row>
     <row r="5">
@@ -993,49 +999,49 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0528</v>
+        <v>-0.0331</v>
       </c>
       <c r="E5">
-        <v>0.0163</v>
+        <v>0.469</v>
       </c>
       <c r="F5">
-        <v>0.0495</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G5">
-        <v>0.1946691116277547</v>
+        <v>0.1188823147166456</v>
       </c>
       <c r="H5">
-        <v>0.1946691116277547</v>
+        <v>0.1188823147166456</v>
       </c>
       <c r="I5">
-        <v>0.1858443302007269</v>
+        <v>0.1064901900429791</v>
       </c>
       <c r="J5">
-        <v>0.1311692275657217</v>
+        <v>0.0738625351984222</v>
       </c>
       <c r="K5">
-        <v>764.1</v>
+        <v>798.6</v>
       </c>
       <c r="L5">
-        <v>0.06255116408526802</v>
+        <v>0.0910427853209754</v>
       </c>
       <c r="M5">
-        <v>388.7</v>
+        <v>461.7</v>
       </c>
       <c r="N5">
-        <v>0.03241165385320947</v>
+        <v>0.03084580438268306</v>
       </c>
       <c r="O5">
-        <v>0.5087030493390917</v>
+        <v>0.5781367392937641</v>
       </c>
       <c r="P5">
-        <v>388.7</v>
+        <v>461.7</v>
       </c>
       <c r="Q5">
-        <v>0.03241165385320947</v>
+        <v>0.03084580438268306</v>
       </c>
       <c r="R5">
-        <v>0.5087030493390917</v>
+        <v>0.5781367392937641</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1044,73 +1050,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3703.2</v>
+        <v>489.7</v>
       </c>
       <c r="V5">
-        <v>0.3087904207594683</v>
+        <v>0.03271646178514163</v>
       </c>
       <c r="W5">
-        <v>0.0869609751101096</v>
+        <v>0.09021791931675686</v>
       </c>
       <c r="X5">
-        <v>0.1014134419459159</v>
+        <v>0.07693267592510547</v>
       </c>
       <c r="Y5">
-        <v>-0.01445246683580635</v>
+        <v>0.01328524339165139</v>
       </c>
       <c r="Z5">
-        <v>0.6181045387845975</v>
+        <v>0.4337637162933988</v>
       </c>
       <c r="AA5">
-        <v>0.08107629490724233</v>
+        <v>0.03203888776251959</v>
       </c>
       <c r="AB5">
-        <v>0.06056270730923632</v>
+        <v>0.07257960346334014</v>
       </c>
       <c r="AC5">
-        <v>0.02051358759800601</v>
+        <v>-0.04054071570082055</v>
       </c>
       <c r="AD5">
-        <v>18183</v>
+        <v>1884.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>18183</v>
+        <v>1884.8</v>
       </c>
       <c r="AG5">
-        <v>14479.8</v>
+        <v>1395.1</v>
       </c>
       <c r="AH5">
-        <v>0.6025729397261363</v>
+        <v>0.1118389822462736</v>
       </c>
       <c r="AI5">
-        <v>0.6717972969977315</v>
+        <v>0.1690676521770331</v>
       </c>
       <c r="AJ5">
-        <v>0.5469772291140962</v>
+        <v>0.085258905708576</v>
       </c>
       <c r="AK5">
-        <v>0.6197748576809485</v>
+        <v>0.130890838298072</v>
       </c>
       <c r="AL5">
-        <v>1177.4</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1177.4</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>7.646341463414634</v>
-      </c>
-      <c r="AO5">
-        <v>1.928146764056395</v>
+        <v>1.807441503644035</v>
       </c>
       <c r="AP5">
-        <v>6.089066442388561</v>
-      </c>
-      <c r="AQ5">
-        <v>1.928146764056395</v>
+        <v>1.337840429612581</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_prop_cas.xlsx
@@ -648,10 +648,10 @@
         <v>0.1352981029810298</v>
       </c>
       <c r="X2">
-        <v>0.07758269821044392</v>
+        <v>0.07756226476131117</v>
       </c>
       <c r="Y2">
-        <v>0.0577154047705859</v>
+        <v>0.05773583821971864</v>
       </c>
       <c r="Z2">
         <v>1.188117656102748</v>
@@ -660,10 +660,10 @@
         <v>0.176262748386754</v>
       </c>
       <c r="AB2">
-        <v>0.07212885924977307</v>
+        <v>0.07211126848728074</v>
       </c>
       <c r="AC2">
-        <v>0.1041338891369809</v>
+        <v>0.1041514798994733</v>
       </c>
       <c r="AD2">
         <v>6892.4</v>
@@ -785,10 +785,10 @@
         <v>0.1352981029810298</v>
       </c>
       <c r="X3">
-        <v>0.07758269821044392</v>
+        <v>0.07756226476131117</v>
       </c>
       <c r="Y3">
-        <v>0.0577154047705859</v>
+        <v>0.05773583821971864</v>
       </c>
       <c r="Z3">
         <v>3.140065913370999</v>
@@ -797,10 +797,10 @@
         <v>0.2279578147231896</v>
       </c>
       <c r="AB3">
-        <v>0.07209558602393173</v>
+        <v>0.07207794632236016</v>
       </c>
       <c r="AC3">
-        <v>0.1558622286992578</v>
+        <v>0.1558798684008294</v>
       </c>
       <c r="AD3">
         <v>1959.6</v>
@@ -922,10 +922,10 @@
         <v>0.1950921607817011</v>
       </c>
       <c r="X4">
-        <v>0.0778235041610951</v>
+        <v>0.07780291589514628</v>
       </c>
       <c r="Y4">
-        <v>0.117268656620606</v>
+        <v>0.1172892448865548</v>
       </c>
       <c r="Z4">
         <v>1.937663015127804</v>
@@ -934,10 +934,10 @@
         <v>0.176262748386754</v>
       </c>
       <c r="AB4">
-        <v>0.07212885924977307</v>
+        <v>0.07211126848728074</v>
       </c>
       <c r="AC4">
-        <v>0.1041338891369809</v>
+        <v>0.1041514798994733</v>
       </c>
       <c r="AD4">
         <v>3048</v>
@@ -1059,10 +1059,10 @@
         <v>0.09021791931675686</v>
       </c>
       <c r="X5">
-        <v>0.07693267592510547</v>
+        <v>0.07691266038250838</v>
       </c>
       <c r="Y5">
-        <v>0.01328524339165139</v>
+        <v>0.01330525893424848</v>
       </c>
       <c r="Z5">
         <v>0.4337637162933988</v>
@@ -1071,10 +1071,10 @@
         <v>0.03203888776251959</v>
       </c>
       <c r="AB5">
-        <v>0.07257960346334014</v>
+        <v>0.07256182643865622</v>
       </c>
       <c r="AC5">
-        <v>-0.04054071570082055</v>
+        <v>-0.04052293867613663</v>
       </c>
       <c r="AD5">
         <v>1884.8</v>
